--- a/Meta data.xlsx
+++ b/Meta data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doaam\Downloads\PhD\virtual_electrochemist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D59A08F-3F87-4005-A305-ED51493663B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CE8DDD-7C3E-4A9C-A733-F24BC3AB310E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76255CE0-2809-4546-A067-BDE560462423}"/>
   </bookViews>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">Catalyst ID </t>
   </si>
   <si>
+    <t>CATALYST STRUCTURE</t>
+  </si>
+  <si>
     <t>47D</t>
-  </si>
-  <si>
-    <t>CATALYST STRUCTURE</t>
   </si>
 </sst>
 </file>
@@ -618,7 +618,7 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -669,7 +669,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
